--- a/光伏配储项目/电价数据/2026/李朗站.xlsx
+++ b/光伏配储项目/电价数据/2026/李朗站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.94545</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.3846</v>
+      </c>
+      <c r="C117" t="n">
+        <v>1.24008</v>
+      </c>
+      <c r="D117" t="n">
+        <v>1.05438</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.5907899999999999</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.88854</v>
+      </c>
+      <c r="G117" t="n">
+        <v>1.53266</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.44157</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45906</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.43144</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42598</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.4245</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.41254</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.40023</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.39969</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38755</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40443</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42753</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41621</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35549</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39434</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38753</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.42014</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39477</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.424</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41705</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42719</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41483</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44687</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.50118</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.40047</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30827</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.31175</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.32784</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.35095</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.37397</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32283</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.34769</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.12246</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.13464</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.35724</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.14077</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.07353</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.11341</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.21269</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.3084</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.28694</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.05085</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.7619199999999999</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>1.18702</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.14778</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21921</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.2294</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.23464</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.21862</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.6768</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.3112200000000001</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.41987</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.14865</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.3267</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.34041</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.2907</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.29832</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.53349</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.68486</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.7759199999999999</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.95517</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.7310800000000001</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.6592</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39448</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.43129</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.43647</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.65823</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>1.1797</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.78759</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.5161</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.36721</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.59662</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.7555299999999999</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.99898</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>1.05692</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.79441</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.33059</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.8712300000000001</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.79648</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.75705</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.5175299999999999</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47953</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.46885</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41573</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42538</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.70823</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.76931</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.87127</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.916</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.49428</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.51471</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50258</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.50281</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.48508</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.39934</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.4672</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37805</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.37822</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.3789</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33625</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.36626</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35169</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35163</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.36466</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.36804</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35154</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.37407</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.40816</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.8769400000000001</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.7202200000000001</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.8157000000000001</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.45625</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.4377799999999999</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.37729</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34751</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.38672</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.42612</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.50869</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.35448</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.33873</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35668</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.32858</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.40022</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.30344</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.33155</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.33828</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.37414</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.50558</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.7767000000000001</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.99074</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.33242</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.52107</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.88801</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.84437</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.49598</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.72305</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.30629</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>1.07461</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>1.02422</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.29464</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.35029</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.37329</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.46948</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.54492</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.49764</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.52201</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.92269</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.62214</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.95357</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>1.3379</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.55655</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.17658</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>1.12778</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.60262</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.5048</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.66018</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.43845</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.4897</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>1.04649</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.38218</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.90213</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.46675</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>1.56152</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.37154</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>1.15481</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.45018</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.78689</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.80774</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44899</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.42812</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.44361</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33354</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37564</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35469</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.3346</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.50769</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.48674</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.48715</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.37793</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.44756</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.41409</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.36857</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38921</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.3827</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36312</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.42763</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44307</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37006</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.3955</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36685</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36773</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35564</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36111</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35167</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36338</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35726</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38346</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.3951</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47208</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.4439</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.43783</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34729</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39425</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35273</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36725</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34737</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.50612</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.6924199999999999</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.9100499999999999</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.82448</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.7629600000000001</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.25071</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.37754</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.36276</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.33035</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.36335</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.39042</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.40526</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.55352</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.495</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.81751</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.39066</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.59061</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.72287</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.8114199999999999</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.52771</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.5479400000000001</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.7989700000000001</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>1.23733</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.6820499999999999</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.59758</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.49343</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.44523</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.42527</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.3944</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.78955</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.52112</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.50408</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.5700700000000001</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.5952799999999999</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.5425</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.56233</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.26491</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.6163</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>1.18135</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.50426</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.53526</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.5763200000000001</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.9815900000000001</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>1.04521</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>1.40706</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.86946</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.84227</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.6792100000000001</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.9358500000000001</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.61024</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.9107799999999999</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.56259</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>1.32044</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.87548</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.5593400000000001</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.48183</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.61554</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.51548</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.4567</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39739</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36204</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34851</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34196</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.5216000000000001</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.49375</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.44448</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.38933</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.38928</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.40106</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.36706</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.38753</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.38566</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.36148</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.44861</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.35992</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.34855</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.36306</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.35748</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.35858</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33744</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33498</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.3316</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33412</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33147</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.35008</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33892</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35104</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.38516</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38848</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.34861</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.37481</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34399</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.39331</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.41596</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.5272899999999999</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35647</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.7670399999999999</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.6460199999999999</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.8880399999999999</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>1.2278</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.81459</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.94875</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>1.43545</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.7099500000000001</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>1.44552</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>1.28508</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>1.19601</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>1.04019</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>1.53513</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.98395</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.3515</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.36298</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.45706</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.60439</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.42404</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.3346</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.32062</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34764</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.47975</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.40461</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.39892</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.96447</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.96787</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.84833</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>1.41141</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>1.48803</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.42802</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.4952</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45025</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.46174</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.39963</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.47412</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.5197000000000001</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>1.04462</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.94448</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>1.47987</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>1.01149</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.89859</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.50075</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.82045</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.76961</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.65665</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.41596</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.55336</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.5486799999999999</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34638</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34156</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31907</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32307</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.32043</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31396</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31812</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.31987</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.31754</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.7262000000000001</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.85138</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38235</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36137</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.36396</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32906</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32802</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33211</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32073</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31901</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31608</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31878</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31852</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31514</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31643</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31289</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.3142799999999999</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.3194</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31604</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.31073</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.31009</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31339</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31467</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.32106</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.32233</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.32001</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.33219</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.44458</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.31221</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.33027</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.32531</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.30806</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31871</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.3038</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.30434</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.19809</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.45267</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.42219</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.21971</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.15551</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.28622</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.38515</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.40146</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.2704</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.18916</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.51246</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.48559</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.0502</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.3796</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.37723</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.22405</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.44593</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.21002</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.06342</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.10162</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.00123</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.00253</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>1.04019</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.26967</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29758</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29995</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.30811</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.33024</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.31902</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31546</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33572</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33585</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33362</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.37788</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.38343</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.3781</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37174</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.3576</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.38976</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39268</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40148</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46145</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.37108</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39065</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.39248</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.48668</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.3525</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.3568</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34438</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35395</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.34445</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36628</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.5915</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.38085</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.40652</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.3893</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.38456</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35198</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.34518</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35162</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.30546</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.30125</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.28906</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.33504</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.27307</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34141</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.33855</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.32924</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.2862</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.31424</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.31203</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.29733</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.29247</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.29375</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.32953</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.3215</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.3347</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.34623</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.3152</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.30658</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10274</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04356</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.0441</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04476</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.35673</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.0152</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.21609</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.05419</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.20487</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.06565</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>0.36199</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04529</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04423</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.07024</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.06848</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04984</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28994</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29329</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29678</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34717</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.3474100000000001</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34068</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36096</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36042</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33163</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.32484</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31312</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31031</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.39575</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.3454100000000001</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32038</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27071</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30939</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29732</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38676</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.37948</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42758</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45538</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41845</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41528</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38677</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40242</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.2943</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31094</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31343</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31269</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34628</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38546</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78523</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9142100000000001</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.8628899999999999</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29622</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35366</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88751</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6316000000000001</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18709</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.8774400000000001</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>1.15071</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33086</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03292</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53079</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79099</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.8470299999999999</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77298</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77755</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87387</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49315</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39868</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.3999</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44995</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.207</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87883</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62186</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53832</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49769</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45582</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43714</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.44963</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41967</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.34726</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39856</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.3629</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38359</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.40945</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.42685</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.33994</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.38712</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.34611</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.3361</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.32959</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.34051</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.3858</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34745</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.44937</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.34719</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.39305</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.38487</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.56021</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.41263</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.5850299999999999</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.70938</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.8767</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.46658</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.39333</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.5536</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.43489</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.82004</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.57308</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.8532999999999999</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87498</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.34176</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.41966</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.63219</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.3303</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30302</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.29431</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.63458</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.59239</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>1.30104</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31056</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35291</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.3304</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32078</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40648</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.3344</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31717</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31908</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31955</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.33633</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31706</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.30929</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30164</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29586</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31137</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31001</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31081</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.28896</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.3009</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.30483</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.3135</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.31138</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.3162</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.34854</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.33118</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.33448</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33237</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.32467</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.32901</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.32726</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.3893</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.39148</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.42478</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.39344</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.37497</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.35869</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.34731</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.9140900000000001</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.35032</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.44513</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.40788</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.39451</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.43884</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.36748</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.39113</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.35267</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.35581</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.34125</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.34045</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.33591</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.32483</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.34902</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.33707</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.31778</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.37888</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.46398</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.34684</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.37015</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.33459</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.3405899999999999</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.34408</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.35654</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.3467</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.35089</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.30803</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.30951</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.32566</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33024</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33172</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.34154</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31276</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31108</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.28829</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31274</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.31037</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.30069</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.18825</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.3043</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.34054</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.3342</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.35763</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.31071</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.2731</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19781</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.30525</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29876</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.32038</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.28156</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.30927</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.3097200000000001</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.34844</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.3568</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.30902</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.30251</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.31101</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.31298</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.31761</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.31017</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.29843</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29598</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30108</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.30901</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.30748</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.2886</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.33794</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25381</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.33863</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.3132</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.32709</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.32914</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.2745</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.33719</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32119</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.32994</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.30229</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.32901</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.37014</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.34094</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.41399</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.10565</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.33366</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42041</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.34523</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44067</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.32779</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.40154</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35197</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.38144</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.37925</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.53712</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.32276</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.8676900000000001</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.44381</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.14012</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.68723</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.7775599999999999</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.63891</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.50978</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.40375</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.44071</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.49068</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.43095</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.41753</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.40577</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.40505</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.4055299999999999</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.46489</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.40526</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.42585</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.39055</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.42644</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.38447</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.4014</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.41958</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.38879</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.41658</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.40694</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.40529</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.40751</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.37906</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.39578</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.39099</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.38027</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.48708</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.35727</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.30982</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.28824</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.3460299999999999</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.35693</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.30593</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.33455</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.30455</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.30854</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.29944</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.52577</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.35729</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.23208</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24841</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.30138</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.15512</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.27444</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.27536</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.01058</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.33544</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30113</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.25997</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.25308</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.3092200000000001</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.28179</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.29587</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.3106</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.28931</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.30486</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.3108399999999999</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.31901</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.31943</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.3113</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.32918</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.33061</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.3885</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.38517</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.34438</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.35309</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.33337</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.32243</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.36041</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.33519</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.34573</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.35526</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.35488</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.3418</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.5442</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.43467</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.78998</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.43598</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.41589</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.36508</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.44148</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.37054</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.35683</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.32518</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.32502</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32067</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.30837</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.39154</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.32092</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.32362</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.30287</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.2972</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.30112</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.29587</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.29697</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.28894</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.29279</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.31081</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.30919</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31165</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.30773</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.28429</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.28436</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.30104</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.31587</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.30321</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.24818</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.29061</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.35162</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.25242</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.31858</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.35727</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.33544</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.33169</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33062</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.31877</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.29928</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31237</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.24262</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.32344</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.27718</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.26494</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.31087</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.35251</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.22914</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.23516</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.31539</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.32288</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.34897</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.23069</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.26258</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.31338</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.31706</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.28271</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.2882</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.30116</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.3035</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.29509</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.23717</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.28381</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.32829</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.24442</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.2908</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.26226</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.32221</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.31219</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.44674</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.34909</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.40162</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31833</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.36469</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.3558</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.42375</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.33477</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.36479</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.33815</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.38066</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.34715</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.36689</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.41922</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.37891</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.37235</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.38022</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.37772</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.42321</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.41089</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.41125</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.41568</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.43824</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.3951</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.38323</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39086</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.38475</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.34452</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.34542</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.32827</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.33553</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.32932</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.49443</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.3829</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.43773</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.4011</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.39436</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.35631</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.36547</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.36427</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.37569</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.37375</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36429</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.36645</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.34941</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.37494</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.35741</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.36442</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.33968</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.33722</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.34437</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.33516</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.33119</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.33554</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.33119</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34049</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.42129</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.35587</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.36502</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.34854</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.33262</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.33081</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.33281</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32152</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.33413</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.34095</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.35524</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29482</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31645</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.32641</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.3207</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.30184</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.3138</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.9205099999999999</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.8674700000000001</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.36604</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.3977</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.25177</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.27835</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30088</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30131</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31806</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31791</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.3176</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.36158</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31352</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.32615</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.29736</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.23953</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.31344</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.30366</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.3207</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.52847</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.54961</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.4244</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.60099</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.5487799999999999</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.4242</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.33462</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.8618300000000001</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.93413</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.37531</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.41329</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34223</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.41252</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.8892100000000001</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>1.12901</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.77967</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>1.16481</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>1.47417</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.37823</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.37271</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.43485</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.43395</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.42836</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.73302</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.34141</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.34429</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.48417</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.35983</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.42477</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.3623</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.3668</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.37081</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.34111</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.34949</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.33599</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.35458</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.46383</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.36469</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.47638</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.36684</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.34309</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.35393</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.34678</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.33885</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.33188</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.33702</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.33616</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.33966</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34079</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.33866</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.33385</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.33268</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.33699</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33245</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.32934</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33377</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.3295</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.33155</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33444</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.33934</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.36265</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.37412</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.36932</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.36276</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.40531</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.33289</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.6944600000000001</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.80528</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.7932400000000001</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.52104</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.7272000000000001</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>1.46361</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>1.14021</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.80914</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.793</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>1.10601</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.76367</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>1.30177</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>1.17251</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>1.20768</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.71468</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>1.12273</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.39293</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>1.30227</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.61997</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>1.49626</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>1.29102</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>1.53402</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>1.69377</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>1.55617</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>1.71037</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>1.3025</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>1.60929</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>1.04951</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.78287</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>1.382</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.7907000000000001</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.75735</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.84605</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.7729600000000001</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.76822</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>1.33842</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.89471</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>1.75302</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.8746799999999999</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.8566</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>1.13138</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.80376</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.66399</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.6149199999999999</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.5225700000000001</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.3686</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.50386</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.24118</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.3702</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.35192</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.33042</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.35819</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.33555</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.31473</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>1.62725</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.31276</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32002</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.94724</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.40037</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.41357</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.33847</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.3233</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33568</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.35317</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.31639</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.39976</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.36622</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.33033</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32531</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.3248</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.31846</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.3161</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.38485</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32711</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.30228</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.2908</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.30328</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31381</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.31698</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.31336</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.30201</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.30683</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.31786</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.3204</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.31324</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.29907</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.32243</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.3118</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.33109</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.34965</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.37329</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.37197</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.32836</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>1.09344</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.3652</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.34258</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.49959</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.34312</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.33212</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.31658</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.33431</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.33414</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.31023</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32701</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.27729</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32562</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.34105</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.31343</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.31923</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32157</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.32815</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33509</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.33106</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.31798</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.30772</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.31061</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.31207</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.8830399999999999</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.33839</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>1.2426</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>1.48233</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>1.15401</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.5352899999999999</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.33183</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.35777</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.37102</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.34042</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.33984</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.90935</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.38465</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.9064500000000001</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.33916</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.35392</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.35818</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.35008</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.35127</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.35083</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.35402</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.36281</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.36613</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.36538</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.36609</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.34858</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.35922</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.35884</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.32875</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.31164</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.34394</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.32601</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34354</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33002</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.34432</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.34331</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.34433</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.34529</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.34476</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.34396</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.3355</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34332</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34017</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.28339</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34095</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.33601</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.33648</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.32417</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.3335</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.33396</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.32864</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.35179</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.32707</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33347</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.3361</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.32623</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.3261</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.33896</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.32538</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.33733</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.33723</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.3302</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.31731</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.33546</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.33079</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.32607</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30094</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.31931</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32253</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32492</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.3232</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31492</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32374</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31504</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31588</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.32413</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32136</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.3286</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31754</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.36969</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.33784</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31926</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.75512</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>1.33102</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.42226</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.55162</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.42688</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.38905</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.41775</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.49966</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.34186</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.36612</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33379</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.35122</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35114</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.5938600000000001</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.38893</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.34768</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35354</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.38974</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.45215</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.35001</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.35268</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.41025</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.34263</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.37118</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.51001</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.42819</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.37241</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.40682</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.63612</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.37631</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.36972</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.65106</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.42959</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.7042999999999999</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.6285599999999999</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.9098999999999999</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.34429</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.7245499999999999</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35317</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33359</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.33482</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32207</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37013</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.36105</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.35589</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35304</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.3527</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.35587</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35196</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.35105</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35282</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.34668</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.35383</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.35046</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.34997</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.34592</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.34943</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.35332</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35365</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34152</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.35295</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35262</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35036</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.35392</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.35392</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.36462</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.35972</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37373</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35041</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35032</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.3450299999999999</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.34572</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35177</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34339</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32555</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>1.48993</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.48459</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.89061</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.5889500000000001</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.95753</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.48012</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.69439</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.34335</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.3408</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>1.02265</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.3722</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.39612</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.29967</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.29399</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.33526</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.29268</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.28559</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.30467</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.34529</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.35556</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.71778</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.3723399999999999</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.34869</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.34588</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.44068</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.34176</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.76978</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.58243</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.9355399999999999</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.79876</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>1.38215</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.74409</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.7220700000000001</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.34876</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.9986900000000001</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.7518400000000001</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.9913099999999999</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.36594</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>1.45482</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>1.42774</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>1.45852</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>1.05371</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>1.01153</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>1.44502</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.92391</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>1.11273</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.9364</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.89828</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.80959</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>1.50316</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>1.42367</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.7762100000000001</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.40843</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.3992</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.3672</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.369</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.3574</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.35117</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34576</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.45687</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.53046</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.47676</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.6209199999999999</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.39706</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.39723</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.38583</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.39086</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.39025</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.39652</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.38284</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.38849</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.39472</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.39291</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.38054</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38179</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.3968</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.37195</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.39514</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.37387</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.37711</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.38037</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.39188</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.37842</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.41623</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.4182</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.50662</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.46167</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.4224</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.45872</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.42089</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.6008300000000001</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>1.32713</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.9820599999999999</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>1.37436</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>1.41098</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>1.49068</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.42839</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.36589</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.34888</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.35691</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.9221200000000001</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.92334</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.94477</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>1.63234</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.8346699999999999</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.86595</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.8570599999999999</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.9364</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>1.18554</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>1.22031</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>1.55124</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.9099400000000001</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.9112</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.90161</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.9009199999999999</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33928</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.3146</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33436</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.33853</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.35859</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.35258</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.35629</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.36139</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.37203</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.34569</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.36576</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.33245</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.39398</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.41412</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.45988</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.42186</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.47402</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.47426</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.50757</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.62625</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.73538</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.8248300000000001</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.5922799999999999</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.71672</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>1.11939</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>1.45953</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.73746</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.76534</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.61813</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.6664800000000001</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>1.66713</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>1.04145</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.44985</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.44611</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.43925</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.39837</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.50789</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.40679</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.41779</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.42849</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.42842</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.41833</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.41981</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41007</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.38217</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.41806</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.37583</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.38235</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.43699</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.3705</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.36514</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.35942</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.35411</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35091</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.35989</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.30087</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.35212</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.34491</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35378</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.35989</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.36427</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.3688</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37346</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.35136</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.35531</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.34908</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37341</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39562</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.3597</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.38185</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.39323</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.38058</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38054</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.3514</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36071</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34006</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.3347</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.34194</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.3699</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.91708</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.88654</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.8832300000000001</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.90332</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.8924099999999999</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>1.41229</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.90438</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.9837100000000001</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.94099</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.99378</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.40607</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.15233</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.21718</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.30168</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29917</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32207</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.34469</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.33757</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.33942</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.34029</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.35878</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.37978</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.38009</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.91349</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.5515099999999999</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.33949</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.42519</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.4114</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.426</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.40204</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.39439</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.35231</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.35579</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.37438</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.38176</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.32774</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.34173</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.36967</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.37186</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.35409</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.36204</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35567</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.37702</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.34061</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.35874</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.32006</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.354</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.33383</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.30079</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.46183</v>
+      </c>
+      <c r="D135" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.3763</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.36076</v>
+      </c>
+      <c r="G135" t="n">
+        <v>1.60267</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.34722</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.31373</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.30243</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.33741</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.28595</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.28332</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.31366</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.28414</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.31701</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.34538</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.31276</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.27083</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.29638</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.30421</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.31142</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.30456</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.30911</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.26311</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.31365</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.26215</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.25717</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.33187</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.29071</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.2841</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.30814</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.2525</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.34377</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.31089</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.30772</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.30383</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.19001</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.28283</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.24483</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.27346</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.26157</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.25786</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.09956</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.31821</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.27621</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.25701</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.03478</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.28979</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.28155</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.19374</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.40403</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.31045</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.3127799999999999</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.30768</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.24867</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.26839</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.25854</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.24016</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27631</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28495</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.27596</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.32301</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.32524</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.31793</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.34086</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.33787</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.34659</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.36432</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.34288</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.41387</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.45292</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.43982</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.37992</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.6782</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.30337</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.354</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.3411</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.35629</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.33478</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.34372</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.36289</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.33794</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.68147</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.43327</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.5099399999999999</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.3765</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.3408</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.32946</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.3406</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.32918</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.31085</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.33323</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.3107</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.32509</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.30285</v>
+      </c>
+      <c r="C136" t="n">
+        <v>1.17765</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.32879</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.32864</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.33133</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.3404700000000001</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.27541</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.29559</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.29112</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.30731</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.24456</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.28809</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.29543</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.29154</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.25383</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.24405</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.24669</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.24667</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.24339</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.24339</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.24536</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.28367</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.24013</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.24339</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.24371</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.28357</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.2442</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.24399</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.32714</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.25096</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.16727</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.2672</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.21443</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01298</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00043</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.00022</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04957</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.14593</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02127</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03957</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01536</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04286</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04075</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04859</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04824000000000001</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02924</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.0494</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00022</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.27451</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04964</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.0493</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03822</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.01884</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04963</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03614</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.20154</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.26489</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.28841</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.2792</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.30489</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.30862</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.24803</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.31133</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.32936</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.3443</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.33723</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.34105</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.31069</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.3152799999999999</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.35073</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.33965</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.34391</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.34076</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.33899</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.3449700000000001</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.3393</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.36606</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.42147</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.35369</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.36831</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.34915</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.34476</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.34414</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.33649</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.34629</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.31395</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.33225</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.73893</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.63566</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.38754</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.43195</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.39496</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.41597</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.42535</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.36152</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.29504</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.33939</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.31148</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.3082</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.3036</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.26575</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.30485</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.28898</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.26386</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.24557</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.28175</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.27001</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.30021</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.2666</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.29061</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.30278</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.32602</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.43696</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.36068</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.34214</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.34655</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.2704</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.36951</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.68521</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.8424400000000001</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.87725</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.85103</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32578</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.38249</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.11391</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.21744</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.29306</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.30664</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.29812</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.30027</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.26598</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.29935</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.34582</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.04863</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.25826</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.27104</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.00085</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.27369</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.00019</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.3117799999999999</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.3139</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.29266</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.05959</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.2865</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.29913</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.28938</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.30272</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25493</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29214</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.47125</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.3217</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.32291</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.34734</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.37794</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.39001</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.34644</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.36108</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.39163</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.50179</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.7922</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.74658</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.77075</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.34263</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.97988</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.7629199999999999</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.8352000000000001</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.79489</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.84041</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.83861</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.8429099999999999</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.94011</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.75522</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.79084</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.7582100000000001</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.39385</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.35597</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.37247</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.3643</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.36414</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.46749</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.61225</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.66201</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.5739299999999999</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.49381</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.4629</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.40338</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.39335</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.38108</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.37393</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.35839</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.33357</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.33813</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32737</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.32061</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.47701</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.32283</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.31789</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.3167</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.30863</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.31308</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.28631</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.34575</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.34269</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.36764</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.46322</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.47505</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.36825</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.38562</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.32217</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.3244</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.33274</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.42599</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.3752799999999999</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.45218</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.36214</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.41393</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.39451</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.35665</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.35331</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.3400899999999999</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.38464</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.34538</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.31649</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.3244</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.33414</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31486</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.26601</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31751</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30863</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30915</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32688</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32443</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.32203</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.34094</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31987</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32785</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31547</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.31684</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32208</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.33494</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.33869</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33368</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32876</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34576</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.34415</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.35456</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.3448</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.35064</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33435</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.36125</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.40077</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.38887</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.3746</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.34772</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.37418</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.37052</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.4277</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.4536</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.71592</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.40382</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.59074</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.4586</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.37753</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.42055</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.41068</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.39011</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.47269</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.35339</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.35729</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.34002</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.34181</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.3383</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.42073</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.42399</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.40838</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.39179</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.3841</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.37729</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.35741</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.3602</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.35273</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.35243</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34614</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.34892</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.34644</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34169</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.35289</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.3368</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.33604</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.33011</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.33199</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33345</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.33352</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.34375</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.33599</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.35181</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.3447</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.35253</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.3454700000000001</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.35514</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.407</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.36663</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.35694</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.5543899999999999</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.76485</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.53969</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.49989</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.5542899999999999</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.44688</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.35973</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.35447</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.35133</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.34793</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.35638</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.47867</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.35411</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.38719</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.35063</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.30475</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.6152000000000001</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.5809299999999999</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.6053099999999999</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.65586</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.48673</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34234</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.56794</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32707</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32472</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.58982</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.35591</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.33023</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33472</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32406</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.34642</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.34604</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.92241</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.47745</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>1.3348</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>1.40447</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>1.06199</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>1.49921</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>1.7399</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.71161</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.55841</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.45779</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.45607</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.9414600000000001</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>1.2699</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>1.55714</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.65543</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.52818</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.3528</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.42137</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.37928</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.3566</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.38102</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.36399</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.23531</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.35646</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.34448</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.35274</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.33811</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.45443</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.38205</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.37829</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.37061</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.36588</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.34698</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.35712</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.36559</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.36141</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36419</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.3517</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.34806</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.34582</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.34713</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.34675</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.34014</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.31944</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.34039</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.3348</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.33273</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.33098</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.3408</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.34018</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.35019</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.37193</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.35308</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.35659</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.34505</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.35117</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.34969</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.38094</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39124</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.3655</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.3539</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43496</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37995</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.3625</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.37463</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.35543</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31055</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36362</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.45922</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.8726</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.50434</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.2926</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.9817899999999999</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.46283</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.7553500000000001</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31621</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33662</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.3437</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32532</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33353</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34173</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33822</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32487</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34422</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.3434</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.3692</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.36572</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.37201</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.5801900000000001</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.37608</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.39538</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.37395</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.37529</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.41838</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.41304</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.51205</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>1.18999</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.70785</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>1.01002</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.63973</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.4757</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>1.27082</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.4811</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>1.37546</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>1.29957</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.8337899999999999</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>1.09766</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>1.00487</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.49257</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.35967</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.36334</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.35288</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.35712</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.30114</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.3579</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.35955</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.34972</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.3402</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.3278</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.33919</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33266</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.33336</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.34331</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.32361</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.36811</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.34311</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33263</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.3404700000000001</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.3373</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.23385</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.32852</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.3384</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.32856</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.33356</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.34646</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.34538</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.33915</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.37574</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.37573</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.35338</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.34107</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.33861</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.33908</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.36417</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.35224</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.33583</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.34574</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.57285</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.81926</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>1.66988</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.85515</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.6868300000000001</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.8236</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.79316</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.91472</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.81959</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.8401900000000001</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34826</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.34131</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.59588</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.49573</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.36216</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.5923099999999999</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>1.53552</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.53074</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.36639</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.37159</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.88693</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.7454400000000001</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.90544</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.48633</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.96449</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.91298</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.95121</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.9157999999999999</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>1.66226</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.39952</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.5250499999999999</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.40677</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.3699</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.42616</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.69041</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.36205</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.36388</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34269</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.42352</v>
+      </c>
+      <c r="D142" t="n">
+        <v>1.27688</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.5592699999999999</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.7847799999999999</v>
+      </c>
+      <c r="G142" t="n">
+        <v>1.61997</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.36682</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.44125</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.37314</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.38413</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.37149</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.36951</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.37239</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.36871</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.36491</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.36942</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.36868</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.36777</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.36832</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.36379</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.35844</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.35914</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.36271</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.36015</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.35942</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.35026</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.35898</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.35373</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.37195</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.35837</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.34576</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.34841</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.35324</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.36061</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.36234</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.35669</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.34262</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.37584</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.36486</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.35742</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.3627</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>1.4067</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.52573</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.34648</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.4437</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.3235</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.34231</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.42286</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>1.06506</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.33913</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.33731</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.6058</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.34606</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>1.7355</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>1.0194</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.36626</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32292</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.33615</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.34997</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32336</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35598</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.35828</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.35496</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.35046</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.37755</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.5662999999999999</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.42686</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.40483</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.388</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.35576</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.36373</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.38317</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.54279</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.63102</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.92077</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.7793600000000001</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.7289600000000001</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.54888</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.38432</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.53959</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.4166</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>1.71983</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.7447699999999999</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.9741000000000001</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>1.30509</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>1.14389</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.63517</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.3573</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.35741</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.35825</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.35897</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34822</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.41515</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.38541</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.36777</v>
+      </c>
+      <c r="F143" t="n">
+        <v>1.37149</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.37657</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.36778</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.36978</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.36329</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.36832</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.35918</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.36068</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.36274</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.35406</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>1.36556</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.35194</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.35822</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.35734</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.35813</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.35401</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.3542</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.35613</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.35504</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.3576</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.34911</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.34289</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>1.35543</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>1.34952</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.31286</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31738</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.31793</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17558</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30603</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29459</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31066</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14526</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19792</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.14172</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.29105</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04456</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.12129</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.32972</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.22579</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.26543</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.15086</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.14373</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.28848</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>1.19573</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>1.30407</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22606</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>1.26199</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.15292</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.35606</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.30763</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.1527</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.31247</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.29924</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.19665</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.14261</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.27957</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.63962</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.32316</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.32158</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.5786699999999999</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.30012</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.33829</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.34868</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.34763</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.49787</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.52081</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.53837</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.38478</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>1.68613</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>1.08277</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.7038300000000001</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.3499</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.5144299999999999</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.39875</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.77228</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.5646599999999999</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.39222</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.41733</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.5720499999999999</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.38862</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.54906</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.40138</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.67638</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.5577799999999999</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.5515599999999999</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.61491</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.39646</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.38356</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38453</v>
       </c>
     </row>
   </sheetData>
